--- a/Traceability Matrix/RTM.xlsx
+++ b/Traceability Matrix/RTM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FARZAN\Desktop\API_Testing_RestfulBooker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FARZAN\Desktop\API_Testing_RestfulBooker\Traceability Matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DDFD10-EB9B-459E-A670-0F761216FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD852D0-11B6-437B-893B-20BAA79B39C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DF9EFE7E-F317-45F0-B948-53C11351E64F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -121,9 +121,6 @@
     <t>TC_23, TC_24, TC_25, TC_26, TC_27</t>
   </si>
   <si>
-    <t>60% Pass / 40% Fail</t>
-  </si>
-  <si>
     <t>REQ-06</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>TC_028, TC_029, TC_030, TC_031</t>
   </si>
   <si>
-    <t>50% Pass / 50% Fail</t>
-  </si>
-  <si>
     <t>REQ-07</t>
   </si>
   <si>
@@ -211,14 +205,14 @@
     <t xml:space="preserve">BUG-003 </t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-004 </t>
+    <t>80% Pass / 20% Fail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,6 +367,12 @@
       <b/>
       <sz val="24"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1118,7 +1118,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="3" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B3" s="6"/>
     </row>
@@ -1140,15 +1140,15 @@
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1294,73 +1294,73 @@
         <v>32</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
@@ -1371,19 +1371,19 @@
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
@@ -1397,6 +1397,7 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>